--- a/Test Data Driven/AI-Generated/Tracking Environment/Common/clickMultipleDynamicObjects.xlsx
+++ b/Test Data Driven/AI-Generated/Tracking Environment/Common/clickMultipleDynamicObjects.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -623,6 +623,170 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
